--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99070</v>
+        <v>99072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106254</v>
+        <v>106256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99072</v>
+        <v>99073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106256</v>
+        <v>106257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99073</v>
+        <v>99074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106257</v>
+        <v>106258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99074</v>
+        <v>99077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106258</v>
+        <v>106256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106256</v>
+        <v>106257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99077</v>
+        <v>99076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99062</v>
+        <v>99061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99062</v>
+        <v>99061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99062</v>
+        <v>99061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99062</v>
+        <v>99061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99076</v>
+        <v>99082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106257</v>
+        <v>106263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99061</v>
+        <v>99067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99061</v>
+        <v>99067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99061</v>
+        <v>99067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99061</v>
+        <v>99067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99082</v>
+        <v>99085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106263</v>
+        <v>106267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99067</v>
+        <v>99070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99067</v>
+        <v>99070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99067</v>
+        <v>99070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99067</v>
+        <v>99070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 13203-2026 artfynd.xlsx
+++ b/artfynd/A 13203-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131599428</v>
       </c>
       <c r="B2" t="n">
-        <v>99085</v>
+        <v>99090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131599462</v>
       </c>
       <c r="B3" t="n">
-        <v>106267</v>
+        <v>106272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131599119</v>
       </c>
       <c r="B4" t="n">
-        <v>99070</v>
+        <v>99075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131599124</v>
       </c>
       <c r="B5" t="n">
-        <v>99070</v>
+        <v>99075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131598878</v>
       </c>
       <c r="B6" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131598880</v>
       </c>
       <c r="B7" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131598876</v>
       </c>
       <c r="B8" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>131599123</v>
       </c>
       <c r="B9" t="n">
-        <v>99070</v>
+        <v>99075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131599121</v>
       </c>
       <c r="B10" t="n">
-        <v>99070</v>
+        <v>99075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131598879</v>
       </c>
       <c r="B11" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>131598877</v>
       </c>
       <c r="B12" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
